--- a/Document/Mahjong_x_Block_SourceSink.xlsx
+++ b/Document/Mahjong_x_Block_SourceSink.xlsx
@@ -1,12 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FC5CC3068B61AB56FC53D159BD7257C3F05AF559" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F19712-171B-49CA-B86E-83CAE654E7F1}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Source &amp; Sink" state="visible" r:id="rId4"/>
+    <sheet name="Source &amp; Sink" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -22,9 +40,6 @@
     <t>Hệ số (base)</t>
   </si>
   <si>
-    <t>Offset (+n trong ln)</t>
-  </si>
-  <si>
     <t>Bonus / lượt dư (đã bỏ, giữ = 0)</t>
   </si>
   <si>
@@ -106,9 +121,6 @@
     <t>Giấy Hoa Tiên</t>
   </si>
   <si>
-    <t>NGUỒN THU (SOURCE) — round(Hệ số × ln(Màn + Offset))</t>
-  </si>
-  <si>
     <t>Sứ Men Lam</t>
   </si>
   <si>
@@ -130,9 +142,6 @@
     <t>Màn chốt chương?</t>
   </si>
   <si>
-    <t>Sàn (log)</t>
-  </si>
-  <si>
     <t>Bonus lượt dư</t>
   </si>
   <si>
@@ -197,52 +206,71 @@
   </si>
   <si>
     <t>TỔNG</t>
+  </si>
+  <si>
+    <t>Tốc độ tăng (growth, POWER)</t>
+  </si>
+  <si>
+    <t>NGUỒN THU (SOURCE) - round(He so x Growth^(Man-1))</t>
+  </si>
+  <si>
+    <t>San (exponential)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF8A5A13"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF8A5A13"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF8A5A13"/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF8A5A13"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF8A5A13"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF6B5C46"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -272,10 +300,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -284,7 +320,6 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -302,8 +337,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -312,22 +348,22 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -346,7 +382,7 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3000</xdr:colOff>
@@ -356,7 +392,7 @@
     <xdr:ext cx="8953500" cy="4133850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -709,9 +745,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P81"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -728,342 +764,342 @@
     <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="N1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="N1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N2" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="2">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" ht="16.8" customHeight="1" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="16.8" customHeight="1" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="16.8" customHeight="1" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N5" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="16.8" customHeight="1" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="16.8" customHeight="1" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="16.8" customHeight="1" spans="14:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="N9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>11</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N11" t="s">
         <v>12</v>
       </c>
-      <c r="P10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N11" t="s">
+      <c r="O11" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" s="4">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N12" t="s">
         <v>13</v>
       </c>
-      <c r="O11" t="s">
-        <v>12</v>
-      </c>
-      <c r="P11" s="5">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="12" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N12" t="s">
+      <c r="O12" t="s">
+        <v>11</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N13" t="s">
         <v>14</v>
       </c>
-      <c r="O12" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" s="5">
+      <c r="O13" t="s">
+        <v>11</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N15" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" t="s">
+        <v>11</v>
+      </c>
+      <c r="P15" s="4">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" t="s">
+        <v>11</v>
+      </c>
+      <c r="P16" s="4">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N18" t="s">
+        <v>19</v>
+      </c>
+      <c r="O18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" t="s">
+        <v>11</v>
+      </c>
+      <c r="P19" s="4">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P20" s="4">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N21" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P21" s="4">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="4">
         <v>1195</v>
       </c>
     </row>
-    <row r="13" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O13" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="5">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="14" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N14" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="5">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="15" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N15" t="s">
-        <v>17</v>
-      </c>
-      <c r="O15" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" s="5">
+    <row r="24" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N24" t="s">
+        <v>26</v>
+      </c>
+      <c r="O24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P24" s="4">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" s="4">
         <v>1670</v>
       </c>
     </row>
-    <row r="16" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N16" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" s="5">
+    <row r="26" spans="1:16" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N26" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="4">
         <v>1550</v>
       </c>
     </row>
-    <row r="17" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O17" t="s">
-        <v>12</v>
-      </c>
-      <c r="P17" s="5">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" t="s">
+        <v>24</v>
+      </c>
+      <c r="P27" s="4">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>24</v>
+      </c>
+      <c r="P28" s="4">
         <v>1790</v>
       </c>
     </row>
-    <row r="18" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N18" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" t="s">
-        <v>12</v>
-      </c>
-      <c r="P18" s="5">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="19" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>12</v>
-      </c>
-      <c r="P19" s="5">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="20" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O20" t="s">
-        <v>12</v>
-      </c>
-      <c r="P20" s="5">
-        <v>2265</v>
-      </c>
-    </row>
-    <row r="21" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P21" s="5">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="22" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N22" t="s">
+    <row r="29" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O22" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N23" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23" s="5">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="24" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N24" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24" s="5">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="25" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N25" t="s">
-        <v>28</v>
-      </c>
-      <c r="O25" t="s">
-        <v>25</v>
-      </c>
-      <c r="P25" s="5">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="26" ht="16.8" customHeight="1" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N26" t="s">
-        <v>29</v>
-      </c>
-      <c r="O26" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="5">
+      <c r="P29" s="5">
         <v>1550</v>
       </c>
     </row>
-    <row r="27" spans="14:16" x14ac:dyDescent="0.25">
-      <c r="N27" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" t="s">
-        <v>25</v>
-      </c>
-      <c r="P27" s="5">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" t="s">
-        <v>32</v>
-      </c>
-      <c r="O28" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28" s="5">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P29" s="6">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1074,43 +1110,51 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <f>MAX(0,B30-C30)</f>
+        <f t="shared" ref="D30:D61" si="0">MAX(0,B30-C30)</f>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <f>IF(MOD(A30,10)=0,1,0)</f>
+        <f t="shared" ref="F30:F61" si="1">IF(MOD(A30,10)=0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="G30">
-        <f>ROUND($O$2*LN(A30+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A30-1),0)</f>
+        <v>9</v>
       </c>
       <c r="H30">
-        <f>D30*$O$4</f>
+        <f t="shared" ref="H30:H61" si="2">D30*$O$4</f>
+        <v>0</v>
       </c>
       <c r="I30">
-        <f>IF(E30=1,$O$5,0)</f>
+        <f t="shared" ref="I30:I61" si="3">IF(E30=1,$O$5,0)</f>
+        <v>0</v>
       </c>
       <c r="J30">
-        <f>G30+H30+I30</f>
+        <f t="shared" ref="J30:J61" si="4">G30+H30+I30</f>
+        <v>9</v>
       </c>
       <c r="K30">
-        <f>IF(F30=1,J30*$O$6,J30)</f>
+        <f t="shared" ref="K30:K61" si="5">IF(F30=1,J30*$O$6,J30)</f>
+        <v>9</v>
       </c>
       <c r="L30">
-        <f>IF(F30=1,G30*$O$6,G30)</f>
+        <f t="shared" ref="L30:L61" si="6">IF(F30=1,G30*$O$6,G30)</f>
+        <v>9</v>
       </c>
       <c r="N30" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O30" t="s">
-        <v>25</v>
-      </c>
-      <c r="P30" s="5">
+        <v>24</v>
+      </c>
+      <c r="P30" s="4">
         <v>2150</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2</v>
       </c>
@@ -1121,43 +1165,51 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <f>MAX(0,B31-C31)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <f>IF(MOD(A31,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G31">
-        <f>ROUND($O$2*LN(A31+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A31-1),0)</f>
+        <v>10</v>
       </c>
       <c r="H31">
-        <f>D31*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I31">
-        <f>IF(E31=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J31">
-        <f>G31+H31+I31</f>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
       <c r="K31">
-        <f>IF(F31=1,J31*$O$6,J31)</f>
+        <f t="shared" si="5"/>
+        <v>25</v>
       </c>
       <c r="L31">
-        <f>IF(F31=1,G31*$O$6,G31)</f>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="N31" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P31" s="5">
+        <v>24</v>
+      </c>
+      <c r="P31" s="4">
         <v>1430</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1168,43 +1220,51 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <f>MAX(0,B32-C32)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <f>IF(MOD(A32,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G32">
-        <f>ROUND($O$2*LN(A32+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A32-1),0)</f>
+        <v>10</v>
       </c>
       <c r="H32">
-        <f>D32*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I32">
-        <f>IF(E32=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J32">
-        <f>G32+H32+I32</f>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
       <c r="K32">
-        <f>IF(F32=1,J32*$O$6,J32)</f>
+        <f t="shared" si="5"/>
+        <v>25</v>
       </c>
       <c r="L32">
-        <f>IF(F32=1,G32*$O$6,G32)</f>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="N32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32" s="5">
+        <v>24</v>
+      </c>
+      <c r="P32" s="4">
         <v>1195</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1215,43 +1275,51 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <f>MAX(0,B33-C33)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <f>IF(MOD(A33,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G33">
-        <f>ROUND($O$2*LN(A33+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A33-1),0)</f>
+        <v>11</v>
       </c>
       <c r="H33">
-        <f>D33*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I33">
-        <f>IF(E33=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J33">
-        <f>G33+H33+I33</f>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="K33">
-        <f>IF(F33=1,J33*$O$6,J33)</f>
+        <f t="shared" si="5"/>
+        <v>26</v>
       </c>
       <c r="L33">
-        <f>IF(F33=1,G33*$O$6,G33)</f>
+        <f t="shared" si="6"/>
+        <v>11</v>
       </c>
       <c r="N33" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O33" t="s">
-        <v>50</v>
-      </c>
-      <c r="P33" s="5">
+        <v>47</v>
+      </c>
+      <c r="P33" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>5</v>
       </c>
@@ -1262,40 +1330,49 @@
         <v>4</v>
       </c>
       <c r="D34">
-        <f>MAX(0,B34-C34)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <f>IF(MOD(A34,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G34">
-        <f>ROUND($O$2*LN(A34+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A34-1),0)</f>
+        <v>12</v>
       </c>
       <c r="H34">
-        <f>D34*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I34">
-        <f>IF(E34=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J34">
-        <f>G34+H34+I34</f>
+        <f t="shared" si="4"/>
+        <v>27</v>
       </c>
       <c r="K34">
-        <f>IF(F34=1,J34*$O$6,J34)</f>
+        <f t="shared" si="5"/>
+        <v>27</v>
       </c>
       <c r="L34">
-        <f>IF(F34=1,G34*$O$6,G34)</f>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P34" s="8">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P34" s="7">
         <f>SUM(P10:P32)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>33590</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>6</v>
       </c>
@@ -1306,40 +1383,49 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <f>MAX(0,B35-C35)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <f>IF(MOD(A35,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G35">
-        <f>ROUND($O$2*LN(A35+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A35-1),0)</f>
+        <v>13</v>
       </c>
       <c r="H35">
-        <f>D35*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I35">
-        <f>IF(E35=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J35">
-        <f>G35+H35+I35</f>
+        <f t="shared" si="4"/>
+        <v>28</v>
       </c>
       <c r="K35">
-        <f>IF(F35=1,J35*$O$6,J35)</f>
+        <f t="shared" si="5"/>
+        <v>28</v>
       </c>
       <c r="L35">
-        <f>IF(F35=1,G35*$O$6,G35)</f>
-      </c>
-      <c r="N35" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P35" s="9">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="8">
         <f>MIN(P11:P21,P23:P32)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>7</v>
       </c>
@@ -1350,40 +1436,49 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <f>MAX(0,B36-C36)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <f>IF(MOD(A36,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G36">
-        <f>ROUND($O$2*LN(A36+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A36-1),0)</f>
+        <v>14</v>
       </c>
       <c r="H36">
-        <f>D36*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I36">
-        <f>IF(E36=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J36">
-        <f>G36+H36+I36</f>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="K36">
-        <f>IF(F36=1,J36*$O$6,J36)</f>
+        <f t="shared" si="5"/>
+        <v>29</v>
       </c>
       <c r="L36">
-        <f>IF(F36=1,G36*$O$6,G36)</f>
+        <f t="shared" si="6"/>
+        <v>14</v>
       </c>
       <c r="N36" t="s">
-        <v>53</v>
-      </c>
-      <c r="P36" s="10">
+        <v>50</v>
+      </c>
+      <c r="P36" s="9">
         <f>P33/5</f>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>8</v>
       </c>
@@ -1394,34 +1489,42 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <f>MAX(0,B37-C37)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <f>IF(MOD(A37,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G37">
-        <f>ROUND($O$2*LN(A37+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A37-1),0)</f>
+        <v>14</v>
       </c>
       <c r="H37">
-        <f>D37*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I37">
-        <f>IF(E37=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J37">
-        <f>G37+H37+I37</f>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="K37">
-        <f>IF(F37=1,J37*$O$6,J37)</f>
+        <f t="shared" si="5"/>
+        <v>29</v>
       </c>
       <c r="L37">
-        <f>IF(F37=1,G37*$O$6,G37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>9</v>
       </c>
@@ -1432,37 +1535,45 @@
         <v>5</v>
       </c>
       <c r="D38">
-        <f>MAX(0,B38-C38)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <f>IF(MOD(A38,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G38">
-        <f>ROUND($O$2*LN(A38+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A38-1),0)</f>
+        <v>15</v>
       </c>
       <c r="H38">
-        <f>D38*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I38">
-        <f>IF(E38=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J38">
-        <f>G38+H38+I38</f>
+        <f t="shared" si="4"/>
+        <v>30</v>
       </c>
       <c r="K38">
-        <f>IF(F38=1,J38*$O$6,J38)</f>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
       <c r="L38">
-        <f>IF(F38=1,G38*$O$6,G38)</f>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>10</v>
       </c>
@@ -1473,40 +1584,49 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <f>MAX(0,B39-C39)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <f>IF(MOD(A39,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G39">
-        <f>ROUND($O$2*LN(A39+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A39-1),0)</f>
+        <v>17</v>
       </c>
       <c r="H39">
-        <f>D39*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I39">
-        <f>IF(E39=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J39">
-        <f>G39+H39+I39</f>
+        <f t="shared" si="4"/>
+        <v>32</v>
       </c>
       <c r="K39">
-        <f>IF(F39=1,J39*$O$6,J39)</f>
+        <f t="shared" si="5"/>
+        <v>64</v>
       </c>
       <c r="L39">
-        <f>IF(F39=1,G39*$O$6,G39)</f>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="N39" t="s">
-        <v>55</v>
-      </c>
-      <c r="P39" s="11">
+        <v>52</v>
+      </c>
+      <c r="P39" s="10">
         <f>K80</f>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>4959</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>11</v>
       </c>
@@ -1517,40 +1637,49 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <f>MAX(0,B40-C40)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40">
-        <f>IF(MOD(A40,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G40">
-        <f>ROUND($O$2*LN(A40+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A40-1),0)</f>
+        <v>18</v>
       </c>
       <c r="H40">
-        <f>D40*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I40">
-        <f>IF(E40=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J40">
-        <f>G40+H40+I40</f>
+        <f t="shared" si="4"/>
+        <v>33</v>
       </c>
       <c r="K40">
-        <f>IF(F40=1,J40*$O$6,J40)</f>
+        <f t="shared" si="5"/>
+        <v>33</v>
       </c>
       <c r="L40">
-        <f>IF(F40=1,G40*$O$6,G40)</f>
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="N40" t="s">
-        <v>56</v>
-      </c>
-      <c r="P40" s="11">
+        <v>53</v>
+      </c>
+      <c r="P40" s="10">
         <f>L80</f>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>12</v>
       </c>
@@ -1561,40 +1690,49 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <f>MAX(0,B41-C41)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <f>IF(MOD(A41,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G41">
-        <f>ROUND($O$2*LN(A41+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A41-1),0)</f>
+        <v>19</v>
       </c>
       <c r="H41">
-        <f>D41*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I41">
-        <f>IF(E41=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J41">
-        <f>G41+H41+I41</f>
+        <f t="shared" si="4"/>
+        <v>34</v>
       </c>
       <c r="K41">
-        <f>IF(F41=1,J41*$O$6,J41)</f>
+        <f t="shared" si="5"/>
+        <v>34</v>
       </c>
       <c r="L41">
-        <f>IF(F41=1,G41*$O$6,G41)</f>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="N41" t="s">
-        <v>57</v>
-      </c>
-      <c r="P41" s="11">
+        <v>54</v>
+      </c>
+      <c r="P41" s="10">
         <f>L81</f>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>13</v>
       </c>
@@ -1605,40 +1743,49 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <f>MAX(0,B42-C42)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <f>IF(MOD(A42,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G42">
-        <f>ROUND($O$2*LN(A42+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A42-1),0)</f>
+        <v>20</v>
       </c>
       <c r="H42">
-        <f>D42*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I42">
-        <f>IF(E42=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J42">
-        <f>G42+H42+I42</f>
+        <f t="shared" si="4"/>
+        <v>35</v>
       </c>
       <c r="K42">
-        <f>IF(F42=1,J42*$O$6,J42)</f>
+        <f t="shared" si="5"/>
+        <v>35</v>
       </c>
       <c r="L42">
-        <f>IF(F42=1,G42*$O$6,G42)</f>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="N42" t="s">
-        <v>58</v>
-      </c>
-      <c r="P42" s="11">
+        <v>55</v>
+      </c>
+      <c r="P42" s="10">
         <f>P35</f>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="17" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>14</v>
       </c>
@@ -1649,40 +1796,49 @@
         <v>8</v>
       </c>
       <c r="D43">
-        <f>MAX(0,B43-C43)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <f>IF(MOD(A43,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G43">
-        <f>ROUND($O$2*LN(A43+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A43-1),0)</f>
+        <v>22</v>
       </c>
       <c r="H43">
-        <f>D43*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I43">
-        <f>IF(E43=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J43">
-        <f>G43+H43+I43</f>
+        <f t="shared" si="4"/>
+        <v>37</v>
       </c>
       <c r="K43">
-        <f>IF(F43=1,J43*$O$6,J43)</f>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
       <c r="L43">
-        <f>IF(F43=1,G43*$O$6,G43)</f>
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>59</v>
-      </c>
-      <c r="P43" s="12">
+        <v>56</v>
+      </c>
+      <c r="P43" s="11" t="str">
         <f>IF(P41&gt;=P42,"PASS ✓","FAIL ✗")</f>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>PASS ✓</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>15</v>
       </c>
@@ -1693,34 +1849,42 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <f>MAX(0,B44-C44)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <f>IF(MOD(A44,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G44">
-        <f>ROUND($O$2*LN(A44+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A44-1),0)</f>
+        <v>23</v>
       </c>
       <c r="H44">
-        <f>D44*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I44">
-        <f>IF(E44=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J44">
-        <f>G44+H44+I44</f>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="K44">
-        <f>IF(F44=1,J44*$O$6,J44)</f>
+        <f t="shared" si="5"/>
+        <v>38</v>
       </c>
       <c r="L44">
-        <f>IF(F44=1,G44*$O$6,G44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>16</v>
       </c>
@@ -1731,39 +1895,47 @@
         <v>9</v>
       </c>
       <c r="D45">
-        <f>MAX(0,B45-C45)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <f>IF(MOD(A45,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G45">
-        <f>ROUND($O$2*LN(A45+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A45-1),0)</f>
+        <v>25</v>
       </c>
       <c r="H45">
-        <f>D45*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I45">
-        <f>IF(E45=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J45">
-        <f>G45+H45+I45</f>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="K45">
-        <f>IF(F45=1,J45*$O$6,J45)</f>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="L45">
-        <f>IF(F45=1,G45*$O$6,G45)</f>
-      </c>
-      <c r="N45" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="N45" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>17</v>
       </c>
@@ -1774,34 +1946,42 @@
         <v>8</v>
       </c>
       <c r="D46">
-        <f>MAX(0,B46-C46)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <f>IF(MOD(A46,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G46">
-        <f>ROUND($O$2*LN(A46+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A46-1),0)</f>
+        <v>27</v>
       </c>
       <c r="H46">
-        <f>D46*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I46">
-        <f>IF(E46=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J46">
-        <f>G46+H46+I46</f>
+        <f t="shared" si="4"/>
+        <v>42</v>
       </c>
       <c r="K46">
-        <f>IF(F46=1,J46*$O$6,J46)</f>
+        <f t="shared" si="5"/>
+        <v>42</v>
       </c>
       <c r="L46">
-        <f>IF(F46=1,G46*$O$6,G46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>18</v>
       </c>
@@ -1812,34 +1992,42 @@
         <v>8</v>
       </c>
       <c r="D47">
-        <f>MAX(0,B47-C47)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <f>IF(MOD(A47,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G47">
-        <f>ROUND($O$2*LN(A47+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A47-1),0)</f>
+        <v>28</v>
       </c>
       <c r="H47">
-        <f>D47*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I47">
-        <f>IF(E47=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J47">
-        <f>G47+H47+I47</f>
+        <f t="shared" si="4"/>
+        <v>43</v>
       </c>
       <c r="K47">
-        <f>IF(F47=1,J47*$O$6,J47)</f>
+        <f t="shared" si="5"/>
+        <v>43</v>
       </c>
       <c r="L47">
-        <f>IF(F47=1,G47*$O$6,G47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>19</v>
       </c>
@@ -1850,34 +2038,42 @@
         <v>9</v>
       </c>
       <c r="D48">
-        <f>MAX(0,B48-C48)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <f>IF(MOD(A48,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G48">
-        <f>ROUND($O$2*LN(A48+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A48-1),0)</f>
+        <v>30</v>
       </c>
       <c r="H48">
-        <f>D48*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I48">
-        <f>IF(E48=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J48">
-        <f>G48+H48+I48</f>
+        <f t="shared" si="4"/>
+        <v>45</v>
       </c>
       <c r="K48">
-        <f>IF(F48=1,J48*$O$6,J48)</f>
+        <f t="shared" si="5"/>
+        <v>45</v>
       </c>
       <c r="L48">
-        <f>IF(F48=1,G48*$O$6,G48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>20</v>
       </c>
@@ -1888,34 +2084,42 @@
         <v>8</v>
       </c>
       <c r="D49">
-        <f>MAX(0,B49-C49)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <f>IF(MOD(A49,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G49">
-        <f>ROUND($O$2*LN(A49+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A49-1),0)</f>
+        <v>33</v>
       </c>
       <c r="H49">
-        <f>D49*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I49">
-        <f>IF(E49=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J49">
-        <f>G49+H49+I49</f>
+        <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="K49">
-        <f>IF(F49=1,J49*$O$6,J49)</f>
+        <f t="shared" si="5"/>
+        <v>96</v>
       </c>
       <c r="L49">
-        <f>IF(F49=1,G49*$O$6,G49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>21</v>
       </c>
@@ -1926,34 +2130,42 @@
         <v>5</v>
       </c>
       <c r="D50">
-        <f>MAX(0,B50-C50)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50">
-        <f>IF(MOD(A50,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G50">
-        <f>ROUND($O$2*LN(A50+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A50-1),0)</f>
+        <v>35</v>
       </c>
       <c r="H50">
-        <f>D50*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I50">
-        <f>IF(E50=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J50">
-        <f>G50+H50+I50</f>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="K50">
-        <f>IF(F50=1,J50*$O$6,J50)</f>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
       <c r="L50">
-        <f>IF(F50=1,G50*$O$6,G50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>22</v>
       </c>
@@ -1964,34 +2176,42 @@
         <v>11</v>
       </c>
       <c r="D51">
-        <f>MAX(0,B51-C51)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <f>IF(MOD(A51,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G51">
-        <f>ROUND($O$2*LN(A51+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A51-1),0)</f>
+        <v>37</v>
       </c>
       <c r="H51">
-        <f>D51*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I51">
-        <f>IF(E51=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J51">
-        <f>G51+H51+I51</f>
+        <f t="shared" si="4"/>
+        <v>52</v>
       </c>
       <c r="K51">
-        <f>IF(F51=1,J51*$O$6,J51)</f>
+        <f t="shared" si="5"/>
+        <v>52</v>
       </c>
       <c r="L51">
-        <f>IF(F51=1,G51*$O$6,G51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>23</v>
       </c>
@@ -2002,34 +2222,42 @@
         <v>11</v>
       </c>
       <c r="D52">
-        <f>MAX(0,B52-C52)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52">
-        <f>IF(MOD(A52,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G52">
-        <f>ROUND($O$2*LN(A52+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A52-1),0)</f>
+        <v>40</v>
       </c>
       <c r="H52">
-        <f>D52*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I52">
-        <f>IF(E52=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J52">
-        <f>G52+H52+I52</f>
+        <f t="shared" si="4"/>
+        <v>55</v>
       </c>
       <c r="K52">
-        <f>IF(F52=1,J52*$O$6,J52)</f>
+        <f t="shared" si="5"/>
+        <v>55</v>
       </c>
       <c r="L52">
-        <f>IF(F52=1,G52*$O$6,G52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>24</v>
       </c>
@@ -2040,34 +2268,42 @@
         <v>6</v>
       </c>
       <c r="D53">
-        <f>MAX(0,B53-C53)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53">
-        <f>IF(MOD(A53,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G53">
-        <f>ROUND($O$2*LN(A53+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A53-1),0)</f>
+        <v>43</v>
       </c>
       <c r="H53">
-        <f>D53*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I53">
-        <f>IF(E53=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J53">
-        <f>G53+H53+I53</f>
+        <f t="shared" si="4"/>
+        <v>58</v>
       </c>
       <c r="K53">
-        <f>IF(F53=1,J53*$O$6,J53)</f>
+        <f t="shared" si="5"/>
+        <v>58</v>
       </c>
       <c r="L53">
-        <f>IF(F53=1,G53*$O$6,G53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>25</v>
       </c>
@@ -2078,34 +2314,42 @@
         <v>5</v>
       </c>
       <c r="D54">
-        <f>MAX(0,B54-C54)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <f>IF(MOD(A54,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G54">
-        <f>ROUND($O$2*LN(A54+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A54-1),0)</f>
+        <v>46</v>
       </c>
       <c r="H54">
-        <f>D54*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I54">
-        <f>IF(E54=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J54">
-        <f>G54+H54+I54</f>
+        <f t="shared" si="4"/>
+        <v>61</v>
       </c>
       <c r="K54">
-        <f>IF(F54=1,J54*$O$6,J54)</f>
+        <f t="shared" si="5"/>
+        <v>61</v>
       </c>
       <c r="L54">
-        <f>IF(F54=1,G54*$O$6,G54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>26</v>
       </c>
@@ -2116,34 +2360,42 @@
         <v>6</v>
       </c>
       <c r="D55">
-        <f>MAX(0,B55-C55)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55">
-        <f>IF(MOD(A55,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G55">
-        <f>ROUND($O$2*LN(A55+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A55-1),0)</f>
+        <v>49</v>
       </c>
       <c r="H55">
-        <f>D55*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I55">
-        <f>IF(E55=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J55">
-        <f>G55+H55+I55</f>
+        <f t="shared" si="4"/>
+        <v>64</v>
       </c>
       <c r="K55">
-        <f>IF(F55=1,J55*$O$6,J55)</f>
+        <f t="shared" si="5"/>
+        <v>64</v>
       </c>
       <c r="L55">
-        <f>IF(F55=1,G55*$O$6,G55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>27</v>
       </c>
@@ -2154,34 +2406,42 @@
         <v>9</v>
       </c>
       <c r="D56">
-        <f>MAX(0,B56-C56)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <f>IF(MOD(A56,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G56">
-        <f>ROUND($O$2*LN(A56+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A56-1),0)</f>
+        <v>52</v>
       </c>
       <c r="H56">
-        <f>D56*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I56">
-        <f>IF(E56=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J56">
-        <f>G56+H56+I56</f>
+        <f t="shared" si="4"/>
+        <v>67</v>
       </c>
       <c r="K56">
-        <f>IF(F56=1,J56*$O$6,J56)</f>
+        <f t="shared" si="5"/>
+        <v>67</v>
       </c>
       <c r="L56">
-        <f>IF(F56=1,G56*$O$6,G56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>28</v>
       </c>
@@ -2192,34 +2452,42 @@
         <v>8</v>
       </c>
       <c r="D57">
-        <f>MAX(0,B57-C57)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57">
-        <f>IF(MOD(A57,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G57">
-        <f>ROUND($O$2*LN(A57+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A57-1),0)</f>
+        <v>56</v>
       </c>
       <c r="H57">
-        <f>D57*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I57">
-        <f>IF(E57=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J57">
-        <f>G57+H57+I57</f>
+        <f t="shared" si="4"/>
+        <v>71</v>
       </c>
       <c r="K57">
-        <f>IF(F57=1,J57*$O$6,J57)</f>
+        <f t="shared" si="5"/>
+        <v>71</v>
       </c>
       <c r="L57">
-        <f>IF(F57=1,G57*$O$6,G57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>29</v>
       </c>
@@ -2230,34 +2498,42 @@
         <v>6</v>
       </c>
       <c r="D58">
-        <f>MAX(0,B58-C58)</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <f>IF(MOD(A58,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G58">
-        <f>ROUND($O$2*LN(A58+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A58-1),0)</f>
+        <v>60</v>
       </c>
       <c r="H58">
-        <f>D58*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I58">
-        <f>IF(E58=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J58">
-        <f>G58+H58+I58</f>
+        <f t="shared" si="4"/>
+        <v>75</v>
       </c>
       <c r="K58">
-        <f>IF(F58=1,J58*$O$6,J58)</f>
+        <f t="shared" si="5"/>
+        <v>75</v>
       </c>
       <c r="L58">
-        <f>IF(F58=1,G58*$O$6,G58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>30</v>
       </c>
@@ -2268,34 +2544,42 @@
         <v>8</v>
       </c>
       <c r="D59">
-        <f>MAX(0,B59-C59)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59">
-        <f>IF(MOD(A59,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G59">
-        <f>ROUND($O$2*LN(A59+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A59-1),0)</f>
+        <v>64</v>
       </c>
       <c r="H59">
-        <f>D59*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I59">
-        <f>IF(E59=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J59">
-        <f>G59+H59+I59</f>
+        <f t="shared" si="4"/>
+        <v>79</v>
       </c>
       <c r="K59">
-        <f>IF(F59=1,J59*$O$6,J59)</f>
+        <f t="shared" si="5"/>
+        <v>158</v>
       </c>
       <c r="L59">
-        <f>IF(F59=1,G59*$O$6,G59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>31</v>
       </c>
@@ -2306,34 +2590,42 @@
         <v>9</v>
       </c>
       <c r="D60">
-        <f>MAX(0,B60-C60)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60">
-        <f>IF(MOD(A60,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G60">
-        <f>ROUND($O$2*LN(A60+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A60-1),0)</f>
+        <v>69</v>
       </c>
       <c r="H60">
-        <f>D60*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I60">
-        <f>IF(E60=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J60">
-        <f>G60+H60+I60</f>
+        <f t="shared" si="4"/>
+        <v>84</v>
       </c>
       <c r="K60">
-        <f>IF(F60=1,J60*$O$6,J60)</f>
+        <f t="shared" si="5"/>
+        <v>84</v>
       </c>
       <c r="L60">
-        <f>IF(F60=1,G60*$O$6,G60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>32</v>
       </c>
@@ -2344,34 +2636,42 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <f>MAX(0,B61-C61)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <f>IF(MOD(A61,10)=0,1,0)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G61">
-        <f>ROUND($O$2*LN(A61+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A61-1),0)</f>
+        <v>73</v>
       </c>
       <c r="H61">
-        <f>D61*$O$4</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I61">
-        <f>IF(E61=1,$O$5,0)</f>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="J61">
-        <f>G61+H61+I61</f>
+        <f t="shared" si="4"/>
+        <v>88</v>
       </c>
       <c r="K61">
-        <f>IF(F61=1,J61*$O$6,J61)</f>
+        <f t="shared" si="5"/>
+        <v>88</v>
       </c>
       <c r="L61">
-        <f>IF(F61=1,G61*$O$6,G61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>33</v>
       </c>
@@ -2382,34 +2682,42 @@
         <v>5</v>
       </c>
       <c r="D62">
-        <f>MAX(0,B62-C62)</f>
+        <f t="shared" ref="D62:D93" si="7">MAX(0,B62-C62)</f>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <f>IF(MOD(A62,10)=0,1,0)</f>
+        <f t="shared" ref="F62:F79" si="8">IF(MOD(A62,10)=0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="G62">
-        <f>ROUND($O$2*LN(A62+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A62-1),0)</f>
+        <v>78</v>
       </c>
       <c r="H62">
-        <f>D62*$O$4</f>
+        <f t="shared" ref="H62:H79" si="9">D62*$O$4</f>
+        <v>0</v>
       </c>
       <c r="I62">
-        <f>IF(E62=1,$O$5,0)</f>
+        <f t="shared" ref="I62:I79" si="10">IF(E62=1,$O$5,0)</f>
+        <v>15</v>
       </c>
       <c r="J62">
-        <f>G62+H62+I62</f>
+        <f t="shared" ref="J62:J93" si="11">G62+H62+I62</f>
+        <v>93</v>
       </c>
       <c r="K62">
-        <f>IF(F62=1,J62*$O$6,J62)</f>
+        <f t="shared" ref="K62:K93" si="12">IF(F62=1,J62*$O$6,J62)</f>
+        <v>93</v>
       </c>
       <c r="L62">
-        <f>IF(F62=1,G62*$O$6,G62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" ref="L62:L79" si="13">IF(F62=1,G62*$O$6,G62)</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>34</v>
       </c>
@@ -2420,34 +2728,42 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <f>MAX(0,B63-C63)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <f>IF(MOD(A63,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G63">
-        <f>ROUND($O$2*LN(A63+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A63-1),0)</f>
+        <v>84</v>
       </c>
       <c r="H63">
-        <f>D63*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I63">
-        <f>IF(E63=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J63">
-        <f>G63+H63+I63</f>
+        <f t="shared" si="11"/>
+        <v>99</v>
       </c>
       <c r="K63">
-        <f>IF(F63=1,J63*$O$6,J63)</f>
+        <f t="shared" si="12"/>
+        <v>99</v>
       </c>
       <c r="L63">
-        <f>IF(F63=1,G63*$O$6,G63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>35</v>
       </c>
@@ -2458,34 +2774,42 @@
         <v>6</v>
       </c>
       <c r="D64">
-        <f>MAX(0,B64-C64)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <f>IF(MOD(A64,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G64">
-        <f>ROUND($O$2*LN(A64+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A64-1),0)</f>
+        <v>90</v>
       </c>
       <c r="H64">
-        <f>D64*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I64">
-        <f>IF(E64=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J64">
-        <f>G64+H64+I64</f>
+        <f t="shared" si="11"/>
+        <v>105</v>
       </c>
       <c r="K64">
-        <f>IF(F64=1,J64*$O$6,J64)</f>
+        <f t="shared" si="12"/>
+        <v>105</v>
       </c>
       <c r="L64">
-        <f>IF(F64=1,G64*$O$6,G64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>36</v>
       </c>
@@ -2496,34 +2820,42 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <f>MAX(0,B65-C65)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65">
-        <f>IF(MOD(A65,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G65">
-        <f>ROUND($O$2*LN(A65+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A65-1),0)</f>
+        <v>96</v>
       </c>
       <c r="H65">
-        <f>D65*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I65">
-        <f>IF(E65=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J65">
-        <f>G65+H65+I65</f>
+        <f t="shared" si="11"/>
+        <v>111</v>
       </c>
       <c r="K65">
-        <f>IF(F65=1,J65*$O$6,J65)</f>
+        <f t="shared" si="12"/>
+        <v>111</v>
       </c>
       <c r="L65">
-        <f>IF(F65=1,G65*$O$6,G65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>37</v>
       </c>
@@ -2534,34 +2866,42 @@
         <v>5</v>
       </c>
       <c r="D66">
-        <f>MAX(0,B66-C66)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <f>IF(MOD(A66,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G66">
-        <f>ROUND($O$2*LN(A66+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A66-1),0)</f>
+        <v>103</v>
       </c>
       <c r="H66">
-        <f>D66*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I66">
-        <f>IF(E66=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J66">
-        <f>G66+H66+I66</f>
+        <f t="shared" si="11"/>
+        <v>118</v>
       </c>
       <c r="K66">
-        <f>IF(F66=1,J66*$O$6,J66)</f>
+        <f t="shared" si="12"/>
+        <v>118</v>
       </c>
       <c r="L66">
-        <f>IF(F66=1,G66*$O$6,G66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>38</v>
       </c>
@@ -2572,34 +2912,42 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <f>MAX(0,B67-C67)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <f>IF(MOD(A67,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G67">
-        <f>ROUND($O$2*LN(A67+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A67-1),0)</f>
+        <v>110</v>
       </c>
       <c r="H67">
-        <f>D67*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I67">
-        <f>IF(E67=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J67">
-        <f>G67+H67+I67</f>
+        <f t="shared" si="11"/>
+        <v>125</v>
       </c>
       <c r="K67">
-        <f>IF(F67=1,J67*$O$6,J67)</f>
+        <f t="shared" si="12"/>
+        <v>125</v>
       </c>
       <c r="L67">
-        <f>IF(F67=1,G67*$O$6,G67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>39</v>
       </c>
@@ -2610,34 +2958,42 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <f>MAX(0,B68-C68)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <f>IF(MOD(A68,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G68">
-        <f>ROUND($O$2*LN(A68+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A68-1),0)</f>
+        <v>118</v>
       </c>
       <c r="H68">
-        <f>D68*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I68">
-        <f>IF(E68=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J68">
-        <f>G68+H68+I68</f>
+        <f t="shared" si="11"/>
+        <v>133</v>
       </c>
       <c r="K68">
-        <f>IF(F68=1,J68*$O$6,J68)</f>
+        <f t="shared" si="12"/>
+        <v>133</v>
       </c>
       <c r="L68">
-        <f>IF(F68=1,G68*$O$6,G68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>40</v>
       </c>
@@ -2648,34 +3004,42 @@
         <v>6</v>
       </c>
       <c r="D69">
-        <f>MAX(0,B69-C69)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <f>IF(MOD(A69,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="G69">
-        <f>ROUND($O$2*LN(A69+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A69-1),0)</f>
+        <v>126</v>
       </c>
       <c r="H69">
-        <f>D69*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I69">
-        <f>IF(E69=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J69">
-        <f>G69+H69+I69</f>
+        <f t="shared" si="11"/>
+        <v>141</v>
       </c>
       <c r="K69">
-        <f>IF(F69=1,J69*$O$6,J69)</f>
+        <f t="shared" si="12"/>
+        <v>282</v>
       </c>
       <c r="L69">
-        <f>IF(F69=1,G69*$O$6,G69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>41</v>
       </c>
@@ -2686,34 +3050,42 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <f>MAX(0,B70-C70)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <f>IF(MOD(A70,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G70">
-        <f>ROUND($O$2*LN(A70+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A70-1),0)</f>
+        <v>135</v>
       </c>
       <c r="H70">
-        <f>D70*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I70">
-        <f>IF(E70=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J70">
-        <f>G70+H70+I70</f>
+        <f t="shared" si="11"/>
+        <v>150</v>
       </c>
       <c r="K70">
-        <f>IF(F70=1,J70*$O$6,J70)</f>
+        <f t="shared" si="12"/>
+        <v>150</v>
       </c>
       <c r="L70">
-        <f>IF(F70=1,G70*$O$6,G70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>42</v>
       </c>
@@ -2724,34 +3096,42 @@
         <v>5</v>
       </c>
       <c r="D71">
-        <f>MAX(0,B71-C71)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <f>IF(MOD(A71,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G71">
-        <f>ROUND($O$2*LN(A71+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A71-1),0)</f>
+        <v>144</v>
       </c>
       <c r="H71">
-        <f>D71*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I71">
-        <f>IF(E71=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J71">
-        <f>G71+H71+I71</f>
+        <f t="shared" si="11"/>
+        <v>159</v>
       </c>
       <c r="K71">
-        <f>IF(F71=1,J71*$O$6,J71)</f>
+        <f t="shared" si="12"/>
+        <v>159</v>
       </c>
       <c r="L71">
-        <f>IF(F71=1,G71*$O$6,G71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>43</v>
       </c>
@@ -2762,34 +3142,42 @@
         <v>9</v>
       </c>
       <c r="D72">
-        <f>MAX(0,B72-C72)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72">
-        <f>IF(MOD(A72,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G72">
-        <f>ROUND($O$2*LN(A72+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A72-1),0)</f>
+        <v>154</v>
       </c>
       <c r="H72">
-        <f>D72*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I72">
-        <f>IF(E72=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J72">
-        <f>G72+H72+I72</f>
+        <f t="shared" si="11"/>
+        <v>169</v>
       </c>
       <c r="K72">
-        <f>IF(F72=1,J72*$O$6,J72)</f>
+        <f t="shared" si="12"/>
+        <v>169</v>
       </c>
       <c r="L72">
-        <f>IF(F72=1,G72*$O$6,G72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>44</v>
       </c>
@@ -2800,34 +3188,42 @@
         <v>8</v>
       </c>
       <c r="D73">
-        <f>MAX(0,B73-C73)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <f>IF(MOD(A73,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G73">
-        <f>ROUND($O$2*LN(A73+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A73-1),0)</f>
+        <v>165</v>
       </c>
       <c r="H73">
-        <f>D73*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I73">
-        <f>IF(E73=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J73">
-        <f>G73+H73+I73</f>
+        <f t="shared" si="11"/>
+        <v>180</v>
       </c>
       <c r="K73">
-        <f>IF(F73=1,J73*$O$6,J73)</f>
+        <f t="shared" si="12"/>
+        <v>180</v>
       </c>
       <c r="L73">
-        <f>IF(F73=1,G73*$O$6,G73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>45</v>
       </c>
@@ -2838,34 +3234,42 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <f>MAX(0,B74-C74)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74">
-        <f>IF(MOD(A74,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G74">
-        <f>ROUND($O$2*LN(A74+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A74-1),0)</f>
+        <v>177</v>
       </c>
       <c r="H74">
-        <f>D74*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I74">
-        <f>IF(E74=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J74">
-        <f>G74+H74+I74</f>
+        <f t="shared" si="11"/>
+        <v>192</v>
       </c>
       <c r="K74">
-        <f>IF(F74=1,J74*$O$6,J74)</f>
+        <f t="shared" si="12"/>
+        <v>192</v>
       </c>
       <c r="L74">
-        <f>IF(F74=1,G74*$O$6,G74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>46</v>
       </c>
@@ -2876,34 +3280,42 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <f>MAX(0,B75-C75)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <f>IF(MOD(A75,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G75">
-        <f>ROUND($O$2*LN(A75+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A75-1),0)</f>
+        <v>189</v>
       </c>
       <c r="H75">
-        <f>D75*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I75">
-        <f>IF(E75=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J75">
-        <f>G75+H75+I75</f>
+        <f t="shared" si="11"/>
+        <v>204</v>
       </c>
       <c r="K75">
-        <f>IF(F75=1,J75*$O$6,J75)</f>
+        <f t="shared" si="12"/>
+        <v>204</v>
       </c>
       <c r="L75">
-        <f>IF(F75=1,G75*$O$6,G75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>47</v>
       </c>
@@ -2914,34 +3326,42 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <f>MAX(0,B76-C76)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76">
-        <f>IF(MOD(A76,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G76">
-        <f>ROUND($O$2*LN(A76+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A76-1),0)</f>
+        <v>202</v>
       </c>
       <c r="H76">
-        <f>D76*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I76">
-        <f>IF(E76=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J76">
-        <f>G76+H76+I76</f>
+        <f t="shared" si="11"/>
+        <v>217</v>
       </c>
       <c r="K76">
-        <f>IF(F76=1,J76*$O$6,J76)</f>
+        <f t="shared" si="12"/>
+        <v>217</v>
       </c>
       <c r="L76">
-        <f>IF(F76=1,G76*$O$6,G76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>48</v>
       </c>
@@ -2952,34 +3372,42 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <f>MAX(0,B77-C77)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77">
-        <f>IF(MOD(A77,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G77">
-        <f>ROUND($O$2*LN(A77+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A77-1),0)</f>
+        <v>216</v>
       </c>
       <c r="H77">
-        <f>D77*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I77">
-        <f>IF(E77=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J77">
-        <f>G77+H77+I77</f>
+        <f t="shared" si="11"/>
+        <v>231</v>
       </c>
       <c r="K77">
-        <f>IF(F77=1,J77*$O$6,J77)</f>
+        <f t="shared" si="12"/>
+        <v>231</v>
       </c>
       <c r="L77">
-        <f>IF(F77=1,G77*$O$6,G77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>49</v>
       </c>
@@ -2990,34 +3418,42 @@
         <v>8</v>
       </c>
       <c r="D78">
-        <f>MAX(0,B78-C78)</f>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
-        <f>IF(MOD(A78,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G78">
-        <f>ROUND($O$2*LN(A78+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A78-1),0)</f>
+        <v>232</v>
       </c>
       <c r="H78">
-        <f>D78*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I78">
-        <f>IF(E78=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J78">
-        <f>G78+H78+I78</f>
+        <f t="shared" si="11"/>
+        <v>247</v>
       </c>
       <c r="K78">
-        <f>IF(F78=1,J78*$O$6,J78)</f>
+        <f t="shared" si="12"/>
+        <v>247</v>
       </c>
       <c r="L78">
-        <f>IF(F78=1,G78*$O$6,G78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>50</v>
       </c>
@@ -3028,54 +3464,65 @@
         <v>8</v>
       </c>
       <c r="D79">
-        <f>MAX(0,B79-C79)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <f>IF(MOD(A79,10)=0,1,0)</f>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="G79">
-        <f>ROUND($O$2*LN(A79+$O$3),0)</f>
+        <f>ROUND($O$2*POWER($O$3,A79-1),0)</f>
+        <v>248</v>
       </c>
       <c r="H79">
-        <f>D79*$O$4</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="I79">
-        <f>IF(E79=1,$O$5,0)</f>
+        <f t="shared" si="10"/>
+        <v>15</v>
       </c>
       <c r="J79">
-        <f>G79+H79+I79</f>
+        <f t="shared" si="11"/>
+        <v>263</v>
       </c>
       <c r="K79">
-        <f>IF(F79=1,J79*$O$6,J79)</f>
+        <f t="shared" si="12"/>
+        <v>526</v>
       </c>
       <c r="L79">
-        <f>IF(F79=1,G79*$O$6,G79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K80" s="14">
+        <f t="shared" si="13"/>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K80" s="12">
         <f>SUM(K30:K79)</f>
-      </c>
-      <c r="L80" s="14">
+        <v>4959</v>
+      </c>
+      <c r="L80" s="12">
         <f>SUM(L30:L79)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>57</v>
-      </c>
-      <c r="L81" s="14">
+        <v>54</v>
+      </c>
+      <c r="L81" s="12">
         <f>SUM(L30:L59)</f>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A29:L79"/>
+  <autoFilter ref="A29:L79" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="N45:P45"/>
@@ -3104,16 +3551,45 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P43">
-    <cfRule type="containsText" dxfId="0" priority="3">
-      <formula>NOT(ISERROR(SEARCH("PASS",P43)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4">
-      <formula>NOT(ISERROR(SEARCH("FAIL",P43)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{00000000-000E-0000-0000-000003000000}">
+            <xm:f>NOT(ISERROR(SEARCH("PASS",P43)))</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{00000000-000E-0000-0000-000004000000}">
+            <xm:f>NOT(ISERROR(SEARCH("FAIL",P43)))</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>P43</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>